--- a/artfynd/A 15278-2024 artfynd.xlsx
+++ b/artfynd/A 15278-2024 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>121326363</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 15278-2024 artfynd.xlsx
+++ b/artfynd/A 15278-2024 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>121326363</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 15278-2024 artfynd.xlsx
+++ b/artfynd/A 15278-2024 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>121326363</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 15278-2024 artfynd.xlsx
+++ b/artfynd/A 15278-2024 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>121326363</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 15278-2024 artfynd.xlsx
+++ b/artfynd/A 15278-2024 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>121326363</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 15278-2024 artfynd.xlsx
+++ b/artfynd/A 15278-2024 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>121326363</v>
       </c>
       <c r="B11" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 15278-2024 artfynd.xlsx
+++ b/artfynd/A 15278-2024 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>121326363</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 15278-2024 artfynd.xlsx
+++ b/artfynd/A 15278-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120659704</v>
+        <v>120660391</v>
       </c>
       <c r="B2" t="n">
-        <v>105161</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gavellös, Gavellös, Upl</t>
+          <t>Länsmansängen, Länsmansängen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>701387</v>
+        <v>701552</v>
       </c>
       <c r="R2" t="n">
-        <v>6665316</v>
+        <v>6665219</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120659839</v>
+        <v>120660593</v>
       </c>
       <c r="B3" t="n">
-        <v>74641</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gavellös, Gavellös, Upl</t>
+          <t>Länsmansängen, Länsmansängen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>701382</v>
+        <v>701561</v>
       </c>
       <c r="R3" t="n">
-        <v>6665342</v>
+        <v>6665229</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,12 +872,7 @@
         <v>120660598</v>
       </c>
       <c r="B4" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,59 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120660296</v>
+        <v>120659847</v>
       </c>
       <c r="B5" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gavellös, Gavellös, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>701411</v>
+        <v>701413</v>
       </c>
       <c r="R5" t="n">
-        <v>6665322</v>
+        <v>6665348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120660391</v>
+        <v>120659839</v>
       </c>
       <c r="B6" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Länsmansängen, Länsmansängen, Upl</t>
+          <t>Gavellös, Gavellös, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701552</v>
+        <v>701382</v>
       </c>
       <c r="R6" t="n">
-        <v>6665219</v>
+        <v>6665342</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120659847</v>
+        <v>120660169</v>
       </c>
       <c r="B7" t="n">
-        <v>91988</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>701413</v>
+        <v>701407</v>
       </c>
       <c r="R7" t="n">
-        <v>6665348</v>
+        <v>6665308</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120661127</v>
+        <v>120660296</v>
       </c>
       <c r="B8" t="n">
-        <v>98056</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,7 +1287,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1345,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>701458</v>
+        <v>701411</v>
       </c>
       <c r="R8" t="n">
-        <v>6665474</v>
+        <v>6665322</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,50 +1363,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120660001</v>
+        <v>120661127</v>
       </c>
       <c r="B9" t="n">
-        <v>100322</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gavellös, Gavellös, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>701387</v>
+        <v>701458</v>
       </c>
       <c r="R9" t="n">
-        <v>6665307</v>
+        <v>6665474</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,50 +1469,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120658881</v>
+        <v>121326363</v>
       </c>
       <c r="B10" t="n">
-        <v>100322</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gavellös, Gavellös, Upl</t>
+          <t>Gavellös 2 (*knärot* /stjälk/), Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>701382</v>
+        <v>701412</v>
       </c>
       <c r="R10" t="n">
-        <v>6665460</v>
+        <v>6665322</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,6 +1541,11 @@
           <t>Häverö</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>AB-Nor-1866</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>2024-10-25</t>
@@ -1585,6 +1554,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gavellös, Obskoord: 6665174/1656705/10 m ().</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1599,7 +1573,7 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -1607,63 +1581,53 @@
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121326363</v>
+        <v>120659704</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gavellös 2 (*knärot* /stjälk/), Upl</t>
+          <t>Gavellös, Gavellös, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>701412</v>
+        <v>701387</v>
       </c>
       <c r="R11" t="n">
-        <v>6665322</v>
+        <v>6665316</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,11 +1652,6 @@
           <t>Häverö</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>AB-Nor-1866</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>2024-10-25</t>
@@ -1701,11 +1660,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gavellös, Obskoord: 6665174/1656705/10 m ().</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1674,7 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
@@ -1728,11 +1682,395 @@
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120659996</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gavellös, Gavellös, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>701378</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6665302</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120658633</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gavellös, Gavellös, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>701425</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6665503</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120658881</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gavellös, Gavellös, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>701382</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6665460</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120660001</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gavellös, Gavellös, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>701387</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6665307</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15278-2024 artfynd.xlsx
+++ b/artfynd/A 15278-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660391</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660593</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660598</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120659847</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120659839</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660169</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660296</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661127</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121326363</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1683,6 +1733,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120659704</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1780,6 +1835,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120659996</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1877,6 +1937,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120658633</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120658881</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2071,8 +2141,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120660001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>